--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/118.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/118.xlsx
@@ -426,13 +426,13 @@
         <v>-16.58610990410861</v>
       </c>
       <c r="E2">
-        <v>-17.08440841190728</v>
+        <v>-12.10743886699125</v>
       </c>
       <c r="F2">
-        <v>-3.779949122351419</v>
+        <v>-3.581483061416893</v>
       </c>
       <c r="G2">
-        <v>-10.83727060620492</v>
+        <v>-8.242882141262113</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.50804135516942</v>
       </c>
       <c r="E3">
-        <v>-17.42912038184515</v>
+        <v>-13.01184305343314</v>
       </c>
       <c r="F3">
-        <v>-3.850564129970465</v>
+        <v>-3.939610312301801</v>
       </c>
       <c r="G3">
-        <v>-11.70142561886642</v>
+        <v>-7.271978587686816</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.46104112360323</v>
       </c>
       <c r="E4">
-        <v>-17.08518730943659</v>
+        <v>-13.29338733943802</v>
       </c>
       <c r="F4">
-        <v>-3.71839976758861</v>
+        <v>-3.743008078023575</v>
       </c>
       <c r="G4">
-        <v>-9.83486390127792</v>
+        <v>-7.52810556442361</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.42922108238472</v>
       </c>
       <c r="E5">
-        <v>-18.02574230388171</v>
+        <v>-13.35234807101789</v>
       </c>
       <c r="F5">
-        <v>-4.001505096271577</v>
+        <v>-3.553634177702177</v>
       </c>
       <c r="G5">
-        <v>-10.21374921715643</v>
+        <v>-7.121371939468752</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.39238274086278</v>
       </c>
       <c r="E6">
-        <v>-18.48241626518523</v>
+        <v>-14.80916268775945</v>
       </c>
       <c r="F6">
-        <v>-4.000506913551204</v>
+        <v>-3.580266189702181</v>
       </c>
       <c r="G6">
-        <v>-10.27585505147316</v>
+        <v>-7.363723736216638</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.31509280364737</v>
       </c>
       <c r="E7">
-        <v>-18.88169181844152</v>
+        <v>-14.82954534926797</v>
       </c>
       <c r="F7">
-        <v>-3.556347909313748</v>
+        <v>-3.608465472828282</v>
       </c>
       <c r="G7">
-        <v>-10.78745351692997</v>
+        <v>-7.487236879741308</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.17863496355044</v>
       </c>
       <c r="E8">
-        <v>-18.95735356216168</v>
+        <v>-14.68299034495774</v>
       </c>
       <c r="F8">
-        <v>-3.842355009008722</v>
+        <v>-3.647389628718428</v>
       </c>
       <c r="G8">
-        <v>-11.03790290806691</v>
+        <v>-6.950296188181374</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.96571775120579</v>
       </c>
       <c r="E9">
-        <v>-20.73919487232978</v>
+        <v>-16.38319232571555</v>
       </c>
       <c r="F9">
-        <v>-3.226750460148658</v>
+        <v>-3.197689674923646</v>
       </c>
       <c r="G9">
-        <v>-10.02451512358615</v>
+        <v>-6.586093141769533</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.64909178487107</v>
       </c>
       <c r="E10">
-        <v>-22.41162372199855</v>
+        <v>-15.72712059690629</v>
       </c>
       <c r="F10">
-        <v>-3.826928322866387</v>
+        <v>-3.066029788290095</v>
       </c>
       <c r="G10">
-        <v>-9.503809347350801</v>
+        <v>-6.936759367471295</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.22623916411843</v>
       </c>
       <c r="E11">
-        <v>-21.4482633324508</v>
+        <v>-17.12733381702598</v>
       </c>
       <c r="F11">
-        <v>-3.340245078006219</v>
+        <v>-2.880254315966459</v>
       </c>
       <c r="G11">
-        <v>-9.526102561012253</v>
+        <v>-6.976638199037355</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.69854205868855</v>
       </c>
       <c r="E12">
-        <v>-20.71693742258208</v>
+        <v>-16.99272945562199</v>
       </c>
       <c r="F12">
-        <v>-3.477517153793736</v>
+        <v>-2.814505966838859</v>
       </c>
       <c r="G12">
-        <v>-10.11064889742691</v>
+        <v>-6.299999106811256</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.06468212157846</v>
       </c>
       <c r="E13">
-        <v>-22.53093542667864</v>
+        <v>-18.55677833686519</v>
       </c>
       <c r="F13">
-        <v>-3.435324260132143</v>
+        <v>-2.792573283114937</v>
       </c>
       <c r="G13">
-        <v>-9.496231508611409</v>
+        <v>-6.342675349358001</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.35231740591006</v>
       </c>
       <c r="E14">
-        <v>-22.54950217011008</v>
+        <v>-18.27797830610895</v>
       </c>
       <c r="F14">
-        <v>-2.897034554444968</v>
+        <v>-2.720448990087989</v>
       </c>
       <c r="G14">
-        <v>-9.329376702886602</v>
+        <v>-5.452370337481801</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.59151290757358</v>
       </c>
       <c r="E15">
-        <v>-21.69564481054182</v>
+        <v>-19.81955237085208</v>
       </c>
       <c r="F15">
-        <v>-2.539029073568273</v>
+        <v>-2.406875479962653</v>
       </c>
       <c r="G15">
-        <v>-9.368100154059457</v>
+        <v>-5.807605116027756</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.8083271945354</v>
       </c>
       <c r="E16">
-        <v>-23.10096614934216</v>
+        <v>-20.01847464858702</v>
       </c>
       <c r="F16">
-        <v>-2.650535609659114</v>
+        <v>-2.229671953523186</v>
       </c>
       <c r="G16">
-        <v>-8.144704602749487</v>
+        <v>-5.119213587137245</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.04989160556698</v>
       </c>
       <c r="E17">
-        <v>-24.29431414831746</v>
+        <v>-21.74434854849431</v>
       </c>
       <c r="F17">
-        <v>-1.626951002878863</v>
+        <v>-1.946000021536703</v>
       </c>
       <c r="G17">
-        <v>-7.552749265417945</v>
+        <v>-4.968444722187757</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.35684442085656</v>
       </c>
       <c r="E18">
-        <v>-27.87094820431559</v>
+        <v>-21.98290403074438</v>
       </c>
       <c r="F18">
-        <v>-2.020320316548472</v>
+        <v>-1.6711394336138</v>
       </c>
       <c r="G18">
-        <v>-8.877470684048388</v>
+        <v>-4.907921328638801</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.756372379230793</v>
       </c>
       <c r="E19">
-        <v>-27.129080006957</v>
+        <v>-21.98023223107985</v>
       </c>
       <c r="F19">
-        <v>-1.807445633009653</v>
+        <v>-1.729862398798256</v>
       </c>
       <c r="G19">
-        <v>-7.573681844862756</v>
+        <v>-4.299615206888799</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.283083805572852</v>
       </c>
       <c r="E20">
-        <v>-26.123056863783</v>
+        <v>-23.78787225766964</v>
       </c>
       <c r="F20">
-        <v>-1.951580732729364</v>
+        <v>-1.158154695347344</v>
       </c>
       <c r="G20">
-        <v>-7.369292073813693</v>
+        <v>-4.845001100119412</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.955459023180728</v>
       </c>
       <c r="E21">
-        <v>-28.50964417835741</v>
+        <v>-24.83387276938337</v>
       </c>
       <c r="F21">
-        <v>-1.68433946817741</v>
+        <v>-0.9157520273683332</v>
       </c>
       <c r="G21">
-        <v>-7.40655226385819</v>
+        <v>-4.227955138145735</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.771477432237576</v>
       </c>
       <c r="E22">
-        <v>-27.28866343098731</v>
+        <v>-25.41268420314776</v>
       </c>
       <c r="F22">
-        <v>-1.769009385519756</v>
+        <v>-0.7544167068968931</v>
       </c>
       <c r="G22">
-        <v>-7.527171990581536</v>
+        <v>-3.924328454011478</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.731052267307975</v>
       </c>
       <c r="E23">
-        <v>-29.34511593345454</v>
+        <v>-25.11399964302385</v>
       </c>
       <c r="F23">
-        <v>-1.29525778418469</v>
+        <v>-0.5504643686536268</v>
       </c>
       <c r="G23">
-        <v>-7.160843573933482</v>
+        <v>-4.364909096559844</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.820861101397192</v>
       </c>
       <c r="E24">
-        <v>-30.03185675248075</v>
+        <v>-26.69470425166725</v>
       </c>
       <c r="F24">
-        <v>-0.6887578214487959</v>
+        <v>-0.4610918095655882</v>
       </c>
       <c r="G24">
-        <v>-7.490716263103081</v>
+        <v>-4.175370432799951</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.010941599108843</v>
       </c>
       <c r="E25">
-        <v>-30.26645887692212</v>
+        <v>-25.86309981337268</v>
       </c>
       <c r="F25">
-        <v>-1.34077574460112</v>
+        <v>-0.3315484016461903</v>
       </c>
       <c r="G25">
-        <v>-7.041177284325447</v>
+        <v>-4.90896746102921</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.274656930142566</v>
       </c>
       <c r="E26">
-        <v>-29.19666349853509</v>
+        <v>-26.52003195224339</v>
       </c>
       <c r="F26">
-        <v>-0.4648675081875483</v>
+        <v>-0.1919842332551268</v>
       </c>
       <c r="G26">
-        <v>-8.294913985502838</v>
+        <v>-4.122163344892784</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.580743748480097</v>
       </c>
       <c r="E27">
-        <v>-29.930459690975</v>
+        <v>-27.39009672028511</v>
       </c>
       <c r="F27">
-        <v>-0.6392289060680106</v>
+        <v>-0.2526720859190241</v>
       </c>
       <c r="G27">
-        <v>-8.222525596741134</v>
+        <v>-4.545697988459444</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.891790636614418</v>
       </c>
       <c r="E28">
-        <v>-30.23889858411143</v>
+        <v>-27.34039671805093</v>
       </c>
       <c r="F28">
-        <v>-0.6430352542838744</v>
+        <v>-0.4961913931570088</v>
       </c>
       <c r="G28">
-        <v>-7.750560982480477</v>
+        <v>-4.454859929407382</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.18178841404453</v>
       </c>
       <c r="E29">
-        <v>-31.56865780561979</v>
+        <v>-26.80092413799117</v>
       </c>
       <c r="F29">
-        <v>-1.174500869306787</v>
+        <v>-0.2124026613667318</v>
       </c>
       <c r="G29">
-        <v>-7.38933411650844</v>
+        <v>-4.335792848541955</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.43185702281731</v>
       </c>
       <c r="E30">
-        <v>-30.10981669675979</v>
+        <v>-27.12647160592859</v>
       </c>
       <c r="F30">
-        <v>-0.8256314525155666</v>
+        <v>-0.2937582807304768</v>
       </c>
       <c r="G30">
-        <v>-6.997352282476575</v>
+        <v>-4.576350329607556</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.62509189929414</v>
       </c>
       <c r="E31">
-        <v>-30.20170849132344</v>
+        <v>-27.83691672214794</v>
       </c>
       <c r="F31">
-        <v>-1.16637955528974</v>
+        <v>-0.3972064587268847</v>
       </c>
       <c r="G31">
-        <v>-7.897671694609071</v>
+        <v>-4.716992235752413</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.75898469708527</v>
       </c>
       <c r="E32">
-        <v>-28.99757366726187</v>
+        <v>-26.97905619155689</v>
       </c>
       <c r="F32">
-        <v>-0.9578057553062557</v>
+        <v>-0.3277230009800622</v>
       </c>
       <c r="G32">
-        <v>-7.54137092039947</v>
+        <v>-4.215226090547237</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.84107146114351</v>
       </c>
       <c r="E33">
-        <v>-29.83947811968689</v>
+        <v>-26.61942289976374</v>
       </c>
       <c r="F33">
-        <v>-1.235904431406703</v>
+        <v>-0.6033125522174296</v>
       </c>
       <c r="G33">
-        <v>-7.414540610244451</v>
+        <v>-4.168176617343114</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.8785574320846</v>
       </c>
       <c r="E34">
-        <v>-28.24331103654429</v>
+        <v>-26.80441559145109</v>
       </c>
       <c r="F34">
-        <v>-1.05146760080599</v>
+        <v>-0.4359607992994567</v>
       </c>
       <c r="G34">
-        <v>-7.30035327350391</v>
+        <v>-4.061527392795494</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.88671901161073</v>
       </c>
       <c r="E35">
-        <v>-29.73815124952826</v>
+        <v>-26.10621999742247</v>
       </c>
       <c r="F35">
-        <v>-1.163456246725261</v>
+        <v>-0.7195416108716312</v>
       </c>
       <c r="G35">
-        <v>-8.425677223758511</v>
+        <v>-4.409137984964508</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.8824947885957</v>
       </c>
       <c r="E36">
-        <v>-27.86471702408103</v>
+        <v>-25.77438247908841</v>
       </c>
       <c r="F36">
-        <v>-1.138015427050483</v>
+        <v>-0.8778500768532418</v>
       </c>
       <c r="G36">
-        <v>-7.544837061579087</v>
+        <v>-4.165932067467489</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.87433905328372</v>
       </c>
       <c r="E37">
-        <v>-28.42320919497301</v>
+        <v>-25.55633192714507</v>
       </c>
       <c r="F37">
-        <v>-1.485307632306772</v>
+        <v>-0.8229293180476346</v>
       </c>
       <c r="G37">
-        <v>-7.755490384788452</v>
+        <v>-4.030729387643653</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.87384731435609</v>
       </c>
       <c r="E38">
-        <v>-27.16948305205344</v>
+        <v>-24.62554937960851</v>
       </c>
       <c r="F38">
-        <v>-0.8641107751104092</v>
+        <v>-0.6472143678309978</v>
       </c>
       <c r="G38">
-        <v>-7.664397413729866</v>
+        <v>-4.203142599328897</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.89075237056474</v>
       </c>
       <c r="E39">
-        <v>-27.87844282879828</v>
+        <v>-25.24519406350007</v>
       </c>
       <c r="F39">
-        <v>-0.8008599537022502</v>
+        <v>-0.5472014294539995</v>
       </c>
       <c r="G39">
-        <v>-7.300015597858904</v>
+        <v>-3.421681703692855</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.92493677623035</v>
       </c>
       <c r="E40">
-        <v>-27.20727316764745</v>
+        <v>-24.57803663032003</v>
       </c>
       <c r="F40">
-        <v>-1.276018951254672</v>
+        <v>-0.745922627548587</v>
       </c>
       <c r="G40">
-        <v>-6.997650231575109</v>
+        <v>-3.624889609984399</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.97818675620669</v>
       </c>
       <c r="E41">
-        <v>-26.42406905954685</v>
+        <v>-24.4777128171541</v>
       </c>
       <c r="F41">
-        <v>-1.49062409429794</v>
+        <v>-0.6165415796401378</v>
       </c>
       <c r="G41">
-        <v>-6.181448471049955</v>
+        <v>-3.023012567671661</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.04869471810026</v>
       </c>
       <c r="E42">
-        <v>-26.91236988331994</v>
+        <v>-24.40338697326621</v>
       </c>
       <c r="F42">
-        <v>-1.341857592429176</v>
+        <v>-0.6009748994067294</v>
       </c>
       <c r="G42">
-        <v>-6.288690283249106</v>
+        <v>-3.260603799934076</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.12671793319831</v>
       </c>
       <c r="E43">
-        <v>-26.21273423455689</v>
+        <v>-24.20073323294895</v>
       </c>
       <c r="F43">
-        <v>-0.8191080592185205</v>
+        <v>-0.5494570738918226</v>
       </c>
       <c r="G43">
-        <v>-6.678288524492697</v>
+        <v>-3.544552601382905</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.20724428404081</v>
       </c>
       <c r="E44">
-        <v>-24.64235907512498</v>
+        <v>-22.57469407101475</v>
       </c>
       <c r="F44">
-        <v>-1.372435118368715</v>
+        <v>-0.7547803601867221</v>
       </c>
       <c r="G44">
-        <v>-7.665403819573804</v>
+        <v>-3.12326912878295</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.28384318579056</v>
       </c>
       <c r="E45">
-        <v>-25.44441522051951</v>
+        <v>-22.12785142678189</v>
       </c>
       <c r="F45">
-        <v>-1.148254876516487</v>
+        <v>-0.631852294346081</v>
       </c>
       <c r="G45">
-        <v>-6.97057327960941</v>
+        <v>-3.772278407938291</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.3463385748871</v>
       </c>
       <c r="E46">
-        <v>-25.24499028216972</v>
+        <v>-22.13460338152733</v>
       </c>
       <c r="F46">
-        <v>-1.081157116889727</v>
+        <v>-0.4048903947552529</v>
       </c>
       <c r="G46">
-        <v>-7.078718870740782</v>
+        <v>-3.234817960728693</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.39237052174367</v>
       </c>
       <c r="E47">
-        <v>-25.08877604280112</v>
+        <v>-21.52792371871973</v>
       </c>
       <c r="F47">
-        <v>-1.07922867757601</v>
+        <v>-0.2435078573418532</v>
       </c>
       <c r="G47">
-        <v>-6.964452080907297</v>
+        <v>-3.339262361947159</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.41965807552268</v>
       </c>
       <c r="E48">
-        <v>-24.17435487185427</v>
+        <v>-20.7432252141966</v>
       </c>
       <c r="F48">
-        <v>-0.9732498371640497</v>
+        <v>-0.5692964731888708</v>
       </c>
       <c r="G48">
-        <v>-6.536633591412821</v>
+        <v>-3.651089267382191</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.42397828415303</v>
       </c>
       <c r="E49">
-        <v>-23.78766394786529</v>
+        <v>-21.11987198283657</v>
       </c>
       <c r="F49">
-        <v>-0.9738735978183577</v>
+        <v>-0.7804771453889655</v>
       </c>
       <c r="G49">
-        <v>-6.708874654730023</v>
+        <v>-3.222463004776133</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.40903883002614</v>
       </c>
       <c r="E50">
-        <v>-23.25931329996837</v>
+        <v>-20.43597730972418</v>
       </c>
       <c r="F50">
-        <v>-1.686698658540583</v>
+        <v>-0.3753143650056994</v>
       </c>
       <c r="G50">
-        <v>-6.443733062489794</v>
+        <v>-3.238909795015232</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.37737315636786</v>
       </c>
       <c r="E51">
-        <v>-22.32397057910608</v>
+        <v>-20.27253562583935</v>
       </c>
       <c r="F51">
-        <v>-1.24886672452571</v>
+        <v>-0.5917386028655149</v>
       </c>
       <c r="G51">
-        <v>-5.856160887452247</v>
+        <v>-3.066662110606952</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.32899031538193</v>
       </c>
       <c r="E52">
-        <v>-22.02856916263773</v>
+        <v>-20.00870673015247</v>
       </c>
       <c r="F52">
-        <v>-0.9829649300640823</v>
+        <v>-0.7894806706899934</v>
       </c>
       <c r="G52">
-        <v>-7.345886516851046</v>
+        <v>-3.607459587720136</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.27044321349028</v>
       </c>
       <c r="E53">
-        <v>-22.01219420062599</v>
+        <v>-19.49714766387599</v>
       </c>
       <c r="F53">
-        <v>-1.426951633881756</v>
+        <v>-0.5573141387073759</v>
       </c>
       <c r="G53">
-        <v>-6.658375593073981</v>
+        <v>-3.590075913093423</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.20433096850981</v>
       </c>
       <c r="E54">
-        <v>-22.05970694991447</v>
+        <v>-18.40336722290733</v>
       </c>
       <c r="F54">
-        <v>-1.352134318428307</v>
+        <v>-0.3965876682769935</v>
       </c>
       <c r="G54">
-        <v>-7.330664628461476</v>
+        <v>-4.091272644465845</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.13002326036993</v>
       </c>
       <c r="E55">
-        <v>-21.96036128713419</v>
+        <v>-18.32067728752727</v>
       </c>
       <c r="F55">
-        <v>-1.300230473703696</v>
+        <v>-0.7124093675335273</v>
       </c>
       <c r="G55">
-        <v>-7.820837243188126</v>
+        <v>-3.745999297447557</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.05237769187289</v>
       </c>
       <c r="E56">
-        <v>-20.7129387800333</v>
+        <v>-18.12195879112269</v>
       </c>
       <c r="F56">
-        <v>-1.517545206521521</v>
+        <v>-0.2094851513740719</v>
       </c>
       <c r="G56">
-        <v>-6.054568502711848</v>
+        <v>-3.376588762902442</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.97169622341838</v>
       </c>
       <c r="E57">
-        <v>-21.22378687589058</v>
+        <v>-18.38151280734632</v>
       </c>
       <c r="F57">
-        <v>-1.608643254909591</v>
+        <v>-0.7378733814955841</v>
       </c>
       <c r="G57">
-        <v>-7.786639307767454</v>
+        <v>-3.895235379812362</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.88662727097423</v>
       </c>
       <c r="E58">
-        <v>-21.09395099761666</v>
+        <v>-17.52126124247922</v>
       </c>
       <c r="F58">
-        <v>-0.6722907058485446</v>
+        <v>-0.4771298308511894</v>
       </c>
       <c r="G58">
-        <v>-7.081900305004021</v>
+        <v>-3.96656108345596</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.80104098835801</v>
       </c>
       <c r="E59">
-        <v>-19.97045923868369</v>
+        <v>-17.21127361123216</v>
       </c>
       <c r="F59">
-        <v>-1.298765091768143</v>
+        <v>-0.3883164197600404</v>
       </c>
       <c r="G59">
-        <v>-7.677937544985484</v>
+        <v>-4.100495824338254</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.71311075466301</v>
       </c>
       <c r="E60">
-        <v>-18.60446316816595</v>
+        <v>-16.13706523492466</v>
       </c>
       <c r="F60">
-        <v>-1.293167813227427</v>
+        <v>-0.5406233639083687</v>
       </c>
       <c r="G60">
-        <v>-7.723977301800129</v>
+        <v>-3.944108963608623</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.61995574432697</v>
       </c>
       <c r="E61">
-        <v>-19.47136706135032</v>
+        <v>-16.66969076228482</v>
       </c>
       <c r="F61">
-        <v>-0.8579311542855249</v>
+        <v>-0.672366915649602</v>
       </c>
       <c r="G61">
-        <v>-7.557274781170128</v>
+        <v>-3.836350706305346</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.52395215387239</v>
       </c>
       <c r="E62">
-        <v>-18.985289718315</v>
+        <v>-16.06553798797351</v>
       </c>
       <c r="F62">
-        <v>-0.9784072526138794</v>
+        <v>-0.7202887982689563</v>
       </c>
       <c r="G62">
-        <v>-8.189903480997156</v>
+        <v>-4.118905768082142</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.42217365322017</v>
       </c>
       <c r="E63">
-        <v>-19.38756764983838</v>
+        <v>-16.33540786798661</v>
       </c>
       <c r="F63">
-        <v>-1.682755629703257</v>
+        <v>-0.6962023592977551</v>
       </c>
       <c r="G63">
-        <v>-8.37221853439036</v>
+        <v>-4.469065480316394</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.31219430381577</v>
       </c>
       <c r="E64">
-        <v>-19.17163642373064</v>
+        <v>-16.14728147228596</v>
       </c>
       <c r="F64">
-        <v>-1.820594308794289</v>
+        <v>-0.8521599185902208</v>
       </c>
       <c r="G64">
-        <v>-8.143631985994762</v>
+        <v>-4.170328471943641</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.19689247910007</v>
       </c>
       <c r="E65">
-        <v>-19.43749407577295</v>
+        <v>-15.63045579073856</v>
       </c>
       <c r="F65">
-        <v>-1.1899507497364</v>
+        <v>-1.113183457416762</v>
       </c>
       <c r="G65">
-        <v>-6.931614779703267</v>
+        <v>-4.920978120245686</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.07254345272521</v>
       </c>
       <c r="E66">
-        <v>-18.58540282106767</v>
+        <v>-15.26108175135491</v>
       </c>
       <c r="F66">
-        <v>-1.122428865999407</v>
+        <v>-0.5199705078217715</v>
       </c>
       <c r="G66">
-        <v>-8.573347418083241</v>
+        <v>-4.468688078124917</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.936819309443935</v>
       </c>
       <c r="E67">
-        <v>-18.05542645100199</v>
+        <v>-14.86530218003254</v>
       </c>
       <c r="F67">
-        <v>-1.358149922507437</v>
+        <v>-0.7921736931164945</v>
       </c>
       <c r="G67">
-        <v>-8.272405586381334</v>
+        <v>-4.970586645151665</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.793030396899974</v>
       </c>
       <c r="E68">
-        <v>-19.01179034820789</v>
+        <v>-14.84275037947434</v>
       </c>
       <c r="F68">
-        <v>-1.959627493680158</v>
+        <v>-0.8244071254942289</v>
       </c>
       <c r="G68">
-        <v>-7.642249864072141</v>
+        <v>-4.962412908215205</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.639291335086895</v>
       </c>
       <c r="E69">
-        <v>-18.96802717539776</v>
+        <v>-14.8108472800903</v>
       </c>
       <c r="F69">
-        <v>-1.528035651310574</v>
+        <v>-0.8613987002336436</v>
       </c>
       <c r="G69">
-        <v>-7.516551760491554</v>
+        <v>-4.81162749053802</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.476380774724753</v>
       </c>
       <c r="E70">
-        <v>-17.92874239063741</v>
+        <v>-14.43295970957224</v>
       </c>
       <c r="F70">
-        <v>-1.657309839824062</v>
+        <v>-0.6793798740817026</v>
       </c>
       <c r="G70">
-        <v>-8.051499503636846</v>
+        <v>-4.796746588338996</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.310165217514268</v>
       </c>
       <c r="E71">
-        <v>-18.72301861768677</v>
+        <v>-15.78335518713354</v>
       </c>
       <c r="F71">
-        <v>-1.409771293947694</v>
+        <v>-1.348477076344947</v>
       </c>
       <c r="G71">
-        <v>-8.303965017007206</v>
+        <v>-4.997110736012305</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.14064785598279</v>
       </c>
       <c r="E72">
-        <v>-16.45988203303545</v>
+        <v>-14.58812334297105</v>
       </c>
       <c r="F72">
-        <v>-1.567577769283208</v>
+        <v>-0.6487791538548862</v>
       </c>
       <c r="G72">
-        <v>-8.03503616067005</v>
+        <v>-4.702051743733683</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.970577160728558</v>
       </c>
       <c r="E73">
-        <v>-18.61565755591291</v>
+        <v>-14.54574588320727</v>
       </c>
       <c r="F73">
-        <v>-1.574747289154438</v>
+        <v>-0.8288446896710259</v>
       </c>
       <c r="G73">
-        <v>-7.647139539833645</v>
+        <v>-4.698439938550337</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.807311782707675</v>
       </c>
       <c r="E74">
-        <v>-19.14780759350228</v>
+        <v>-14.59066381688936</v>
       </c>
       <c r="F74">
-        <v>-1.700737829283229</v>
+        <v>-1.134325878638414</v>
       </c>
       <c r="G74">
-        <v>-8.577469047279633</v>
+        <v>-4.936742938103696</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.65142380249099</v>
       </c>
       <c r="E75">
-        <v>-20.3806076580324</v>
+        <v>-15.21389505219499</v>
       </c>
       <c r="F75">
-        <v>-1.378778755939353</v>
+        <v>-1.474308569932401</v>
       </c>
       <c r="G75">
-        <v>-7.600520437549628</v>
+        <v>-4.633093080150664</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.505485108912088</v>
       </c>
       <c r="E76">
-        <v>-18.8157889362079</v>
+        <v>-15.74941880292006</v>
       </c>
       <c r="F76">
-        <v>-1.854003194516596</v>
+        <v>-1.453100707685928</v>
       </c>
       <c r="G76">
-        <v>-8.173410343120507</v>
+        <v>-5.057425565192288</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.37574775028695</v>
       </c>
       <c r="E77">
-        <v>-19.14248210806925</v>
+        <v>-15.91461300624587</v>
       </c>
       <c r="F77">
-        <v>-2.266921150524871</v>
+        <v>-1.297737087821269</v>
       </c>
       <c r="G77">
-        <v>-6.786026918522738</v>
+        <v>-4.87244552263997</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.261179024850012</v>
       </c>
       <c r="E78">
-        <v>-19.79191962245728</v>
+        <v>-15.46220033898357</v>
       </c>
       <c r="F78">
-        <v>-2.679630357947641</v>
+        <v>-1.186652190738453</v>
       </c>
       <c r="G78">
-        <v>-8.010822830595821</v>
+        <v>-5.117319955088782</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.16203873920999</v>
       </c>
       <c r="E79">
-        <v>-19.89832970468951</v>
+        <v>-16.27380250758627</v>
       </c>
       <c r="F79">
-        <v>-1.74826540901885</v>
+        <v>-1.502118520379186</v>
       </c>
       <c r="G79">
-        <v>-7.529886637923738</v>
+        <v>-5.042584389539734</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.082528652555473</v>
       </c>
       <c r="E80">
-        <v>-20.02364163742977</v>
+        <v>-16.85208410989176</v>
       </c>
       <c r="F80">
-        <v>-2.335442873717044</v>
+        <v>-1.800080618431362</v>
       </c>
       <c r="G80">
-        <v>-8.03566847486805</v>
+        <v>-4.018821355338895</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.019682168497997</v>
       </c>
       <c r="E81">
-        <v>-20.3604151924322</v>
+        <v>-16.71325468223861</v>
       </c>
       <c r="F81">
-        <v>-2.572940778304079</v>
+        <v>-1.547405366290235</v>
       </c>
       <c r="G81">
-        <v>-7.526437049471817</v>
+        <v>-4.318409173915241</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.972035319931294</v>
       </c>
       <c r="E82">
-        <v>-20.9077084471032</v>
+        <v>-18.02852731539643</v>
       </c>
       <c r="F82">
-        <v>-2.537576117143762</v>
+        <v>-1.649123084782194</v>
       </c>
       <c r="G82">
-        <v>-7.924884378941879</v>
+        <v>-5.248384452988528</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.943334149560337</v>
       </c>
       <c r="E83">
-        <v>-22.13250669806177</v>
+        <v>-19.19610376879408</v>
       </c>
       <c r="F83">
-        <v>-2.663039815604372</v>
+        <v>-1.696621671658718</v>
       </c>
       <c r="G83">
-        <v>-7.309291746459942</v>
+        <v>-4.321567434359705</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.930742002850323</v>
       </c>
       <c r="E84">
-        <v>-22.46511858545115</v>
+        <v>-19.27153456033984</v>
       </c>
       <c r="F84">
-        <v>-2.234218862197152</v>
+        <v>-1.787191221643802</v>
       </c>
       <c r="G84">
-        <v>-7.049317915806514</v>
+        <v>-4.329489569835181</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.932836948834133</v>
       </c>
       <c r="E85">
-        <v>-23.85359400094297</v>
+        <v>-20.85101648100118</v>
       </c>
       <c r="F85">
-        <v>-2.069618945791279</v>
+        <v>-1.721976341123605</v>
       </c>
       <c r="G85">
-        <v>-6.844782480753723</v>
+        <v>-4.363558393979821</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.95557889716182</v>
       </c>
       <c r="E86">
-        <v>-24.56883929961045</v>
+        <v>-21.62819771867158</v>
       </c>
       <c r="F86">
-        <v>-2.703884127134208</v>
+        <v>-2.027055771900635</v>
       </c>
       <c r="G86">
-        <v>-8.289991204285942</v>
+        <v>-4.412054575584605</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.999245710389997</v>
       </c>
       <c r="E87">
-        <v>-24.9984918565102</v>
+        <v>-23.24186056114281</v>
       </c>
       <c r="F87">
-        <v>-2.591971691015994</v>
+        <v>-2.081814999062697</v>
       </c>
       <c r="G87">
-        <v>-7.434821012218027</v>
+        <v>-4.861709423456114</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.064127107373581</v>
       </c>
       <c r="E88">
-        <v>-26.07025032837955</v>
+        <v>-22.92742143994621</v>
       </c>
       <c r="F88">
-        <v>-2.992579279051266</v>
+        <v>-2.557902596473656</v>
       </c>
       <c r="G88">
-        <v>-6.762654467015484</v>
+        <v>-4.813226484033487</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.159958166790474</v>
       </c>
       <c r="E89">
-        <v>-27.59279574534245</v>
+        <v>-25.17278829259142</v>
       </c>
       <c r="F89">
-        <v>-2.766008368874559</v>
+        <v>-2.377060880401094</v>
       </c>
       <c r="G89">
-        <v>-7.146177857194511</v>
+        <v>-4.76375038094908</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.289793404580378</v>
       </c>
       <c r="E90">
-        <v>-29.5104595764226</v>
+        <v>-26.71882743270611</v>
       </c>
       <c r="F90">
-        <v>-3.214155962156495</v>
+        <v>-2.452671771826424</v>
       </c>
       <c r="G90">
-        <v>-8.918534690917509</v>
+        <v>-4.598878592002296</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.45433401172029</v>
       </c>
       <c r="E91">
-        <v>-31.7945448818334</v>
+        <v>-28.00541218302534</v>
       </c>
       <c r="F91">
-        <v>-3.622750668689559</v>
+        <v>-2.433981318117059</v>
       </c>
       <c r="G91">
-        <v>-8.285250503073705</v>
+        <v>-5.014428199728234</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.664356624878433</v>
       </c>
       <c r="E92">
-        <v>-31.89429584303736</v>
+        <v>-30.0902219897286</v>
       </c>
       <c r="F92">
-        <v>-3.75886385848056</v>
+        <v>-3.058417920225771</v>
       </c>
       <c r="G92">
-        <v>-9.94628693249317</v>
+        <v>-5.573781284589033</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.920599885922794</v>
       </c>
       <c r="E93">
-        <v>-33.48710279846626</v>
+        <v>-31.72997337095802</v>
       </c>
       <c r="F93">
-        <v>-3.288564892480363</v>
+        <v>-2.518398583401551</v>
       </c>
       <c r="G93">
-        <v>-8.690828747635358</v>
+        <v>-5.249824540298111</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.217771833062436</v>
       </c>
       <c r="E94">
-        <v>-35.50730486650209</v>
+        <v>-33.51629787039371</v>
       </c>
       <c r="F94">
-        <v>-3.486427073578247</v>
+        <v>-2.883396313525277</v>
       </c>
       <c r="G94">
-        <v>-8.947816466212362</v>
+        <v>-5.461977540636766</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.558814375497912</v>
       </c>
       <c r="E95">
-        <v>-37.31569209130315</v>
+        <v>-36.20645144007231</v>
       </c>
       <c r="F95">
-        <v>-3.260130353011867</v>
+        <v>-2.911458087662513</v>
       </c>
       <c r="G95">
-        <v>-8.903683583628338</v>
+        <v>-5.10011504992119</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.935265487036096</v>
       </c>
       <c r="E96">
-        <v>-38.49544787554443</v>
+        <v>-38.34432590519746</v>
       </c>
       <c r="F96">
-        <v>-3.639443100223372</v>
+        <v>-3.092617896817751</v>
       </c>
       <c r="G96">
-        <v>-8.712857117653668</v>
+        <v>-6.271574762811074</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.32840419646326</v>
       </c>
       <c r="E97">
-        <v>-39.3130593291553</v>
+        <v>-39.24278873374128</v>
       </c>
       <c r="F97">
-        <v>-3.770742647036705</v>
+        <v>-3.190984040797984</v>
       </c>
       <c r="G97">
-        <v>-9.548892356504597</v>
+        <v>-6.223091823388447</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.7360087039076</v>
       </c>
       <c r="E98">
-        <v>-42.94488869059592</v>
+        <v>-42.11557339591222</v>
       </c>
       <c r="F98">
-        <v>-3.746140135173559</v>
+        <v>-3.081208792578994</v>
       </c>
       <c r="G98">
-        <v>-9.244322166891648</v>
+        <v>-5.989658636323357</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.13006719105323</v>
       </c>
       <c r="E99">
-        <v>-45.69002246320164</v>
+        <v>-44.08891255067967</v>
       </c>
       <c r="F99">
-        <v>-4.3962097381945</v>
+        <v>-3.330764413081178</v>
       </c>
       <c r="G99">
-        <v>-9.546058529522981</v>
+        <v>-7.197415170505812</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.50259871192854</v>
       </c>
       <c r="E100">
-        <v>-46.57459646196394</v>
+        <v>-46.41376997181853</v>
       </c>
       <c r="F100">
-        <v>-3.944388335481149</v>
+        <v>-3.478175705878961</v>
       </c>
       <c r="G100">
-        <v>-9.273494694183704</v>
+        <v>-6.703197069130173</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.82390926081864</v>
       </c>
       <c r="E101">
-        <v>-50.13810813240634</v>
+        <v>-48.47858769789643</v>
       </c>
       <c r="F101">
-        <v>-3.827043465935376</v>
+        <v>-3.455190167186081</v>
       </c>
       <c r="G101">
-        <v>-9.223429313993307</v>
+        <v>-7.007522278373216</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.11240347568328</v>
       </c>
       <c r="E102">
-        <v>-51.51196789803839</v>
+        <v>-50.79942723047198</v>
       </c>
       <c r="F102">
-        <v>-3.8503967997551</v>
+        <v>-3.57986940171624</v>
       </c>
       <c r="G102">
-        <v>-9.364650565607537</v>
+        <v>-6.604900350978133</v>
       </c>
     </row>
   </sheetData>
